--- a/Sheet/AI/프로젝트 mos.A.I.c_대화툴_데이터테이블_0.01.xlsx
+++ b/Sheet/AI/프로젝트 mos.A.I.c_대화툴_데이터테이블_0.01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\Moumi_moz.A.I.c_Documents\Sheet\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4078DBC7-BCD9-46CF-BE9E-7C282FDFDD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112D8965-6F44-4AC8-B145-E6AE3F230FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="687" firstSheet="15" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="2025" windowWidth="21480" windowHeight="13380" tabRatio="687" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="788">
   <si>
     <t>구분</t>
   </si>
@@ -548,9 +548,6 @@
     <t>보조 기억</t>
   </si>
   <si>
-    <t>프로젝트 전체에서 쓰는 변수/플래그 키 사전. 조건식과 엔딩 판정에서 참조하는 이름은 여기서만 정의하는 걸 권장.</t>
-  </si>
-  <si>
     <t>필드명</t>
   </si>
   <si>
@@ -1911,9 +1908,6 @@
   </si>
   <si>
     <t>감정형</t>
-  </si>
-  <si>
-    <t>정체 시간과 실패 횟수에 따라 힌트 직설도/개입성을 점진적으로 보정하는 규칙.</t>
   </si>
   <si>
     <t>HINT_TIME_01</t>
@@ -2521,12 +2515,24 @@
 감정 기복이 거의 없다.
 "또 뭔가 잃어버린 것 같아… 찾긴 해야 하는데… 그냥 어디 있는지 모르겠네."</t>
   </si>
+  <si>
+    <t>정체 시간과 실패 횟수에 따라 힌트 직설도/개입성을 점진적으로 보정하는 규칙.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HintStyleRule</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트 전체에서 쓰는 변수/플래그 키 사전. 조건식과 엔딩 판정에서 참조하는 이름은 여기서만 정의하는 걸 권장.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2567,6 +2573,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -2678,7 +2691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2766,6 +2779,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4250,7 +4266,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -4260,10 +4276,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -4275,204 +4291,204 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>398</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>399</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>401</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="E7" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>405</v>
-      </c>
       <c r="E8" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>407</v>
-      </c>
       <c r="E9" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>410</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>412</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>414</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>415</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>418</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>419</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>420</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -4514,7 +4530,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -4524,10 +4540,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -4539,39 +4555,39 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>134</v>
@@ -4580,109 +4596,109 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>430</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>431</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>432</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>433</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -4727,7 +4743,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -4737,10 +4753,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -4752,281 +4768,281 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>437</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>438</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>439</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>175</v>
-      </c>
       <c r="E7" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>441</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>442</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>103</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D9" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>444</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>445</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>447</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>449</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>103</v>
       </c>
       <c r="E16" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>453</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>454</v>
       </c>
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>103</v>
       </c>
       <c r="E17" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>457</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>458</v>
       </c>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>101</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>103</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="G19" s="18" t="s">
         <v>462</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>463</v>
       </c>
       <c r="H19" s="18"/>
     </row>
@@ -5070,7 +5086,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -5080,10 +5096,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -5095,223 +5111,223 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>466</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>467</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>469</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>470</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>472</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>473</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D8" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>477</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>478</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>480</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>481</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E15" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="F15" s="18" t="s">
         <v>483</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>484</v>
       </c>
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="D16" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="E16" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="F16" s="18" t="s">
         <v>489</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>490</v>
       </c>
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="C17" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="D17" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="E17" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="F17" s="18" t="s">
         <v>495</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>496</v>
       </c>
       <c r="G17" s="18"/>
     </row>
@@ -5355,7 +5371,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -5365,10 +5381,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -5380,39 +5396,39 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>498</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>499</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>500</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>501</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>117</v>
@@ -5421,70 +5437,70 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>503</v>
-      </c>
       <c r="E7" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>505</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>506</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>508</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>509</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>510</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>511</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>119</v>
@@ -5493,74 +5509,74 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>513</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>514</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>515</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>516</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B16" s="18" t="b">
         <v>1</v>
@@ -5569,27 +5585,27 @@
         <v>80</v>
       </c>
       <c r="D16" s="18" t="s">
+        <v>693</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>694</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>690</v>
+      </c>
+      <c r="G16" s="18" t="s">
         <v>695</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="H16" s="18" t="s">
         <v>696</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>692</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>697</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -5598,10 +5614,10 @@
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -5648,7 +5664,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -5658,10 +5674,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -5673,39 +5689,39 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>519</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>500</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>501</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>117</v>
@@ -5714,50 +5730,50 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>521</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>522</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>523</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>524</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>525</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>127</v>
@@ -5766,16 +5782,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>527</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>127</v>
@@ -5784,34 +5800,34 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>529</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>530</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>531</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>532</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>122</v>
@@ -5820,107 +5836,107 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>534</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>535</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>537</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>538</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>117</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18" t="s">
@@ -5930,33 +5946,33 @@
         <v>127</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>122</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>119</v>
       </c>
       <c r="C20" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>542</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>543</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>129</v>
@@ -5965,19 +5981,19 @@
         <v>131</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>124</v>
       </c>
       <c r="I20" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>545</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="K20" s="18" t="s">
         <v>546</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -6018,7 +6034,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6028,10 +6044,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -6043,98 +6059,98 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>550</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>551</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D7" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>552</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>553</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>555</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E9" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F9" s="9"/>
     </row>
@@ -6181,7 +6197,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6191,10 +6207,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -6206,266 +6222,266 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>560</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>561</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>563</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>564</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>567</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>571</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>574</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>575</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>577</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>579</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>580</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>582</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>584</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>587</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>590</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>591</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
+        <v>765</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="D19" s="18" t="s">
         <v>768</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>769</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>770</v>
       </c>
       <c r="E19" s="18">
         <v>-2</v>
@@ -6483,24 +6499,24 @@
         <v>-2</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E20" s="18">
         <v>0</v>
@@ -6518,24 +6534,24 @@
         <v>2</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E21" s="18">
         <v>-1</v>
@@ -6553,24 +6569,24 @@
         <v>-2</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E22" s="18">
         <v>1</v>
@@ -6588,24 +6604,24 @@
         <v>1</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E23" s="18">
         <v>-2</v>
@@ -6623,24 +6639,24 @@
         <v>-1</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E24" s="18">
         <v>-1</v>
@@ -6658,10 +6674,10 @@
         <v>-1</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -6702,7 +6718,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6712,10 +6728,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -6727,222 +6743,222 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>594</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>595</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>385</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>386</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>597</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>598</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>600</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>601</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>603</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>604</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>606</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>608</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>610</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>612</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>613</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>615</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>617</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>618</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -6984,7 +7000,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>619</v>
+        <v>785</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6994,10 +7010,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -7009,150 +7025,150 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>621</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>623</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>624</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>626</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -7191,7 +7207,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -7691,8 +7707,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
-        <v>79</v>
+      <c r="A1" s="31" t="s">
+        <v>786</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -7702,7 +7718,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -7712,10 +7728,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -7727,202 +7743,202 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>634</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>636</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>637</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>640</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>642</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>643</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>645</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>648</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>649</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="E14" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="18" t="s">
         <v>650</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>651</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>652</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>653</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="E15" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="18" t="s">
         <v>654</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>655</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>656</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="E16" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F16" s="18" t="s">
         <v>658</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>659</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -7956,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -7976,15 +7992,15 @@
         <v>15</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
       <c r="F2" s="16" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -7992,7 +8008,7 @@
         <v>51</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>101</v>
@@ -8001,10 +8017,10 @@
         <v>103</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -8012,15 +8028,15 @@
         <v>55</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -8028,19 +8044,19 @@
         <v>58</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>668</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8048,19 +8064,19 @@
         <v>61</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C6" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>670</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>671</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="F6" s="16" t="s">
         <v>672</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8068,19 +8084,19 @@
         <v>38</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>675</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="F7" s="16" t="s">
         <v>676</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>677</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8088,19 +8104,19 @@
         <v>42</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C8" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>679</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>681</v>
-      </c>
       <c r="F8" s="16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -8108,19 +8124,19 @@
         <v>72</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>682</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="F9" s="16" t="s">
         <v>683</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>684</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -8128,19 +8144,19 @@
         <v>76</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>686</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="F10" s="16" t="s">
         <v>687</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>688</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -8175,7 +8191,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>164</v>
+        <v>787</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -8185,10 +8201,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -8200,259 +8216,259 @@
         <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E15" s="5">
         <v>0</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G16" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G17" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -8460,82 +8476,82 @@
         <v>126</v>
       </c>
       <c r="B19" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C19" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G19" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>523</v>
+      </c>
+      <c r="B20" t="s">
         <v>524</v>
       </c>
-      <c r="B20" t="s">
-        <v>525</v>
-      </c>
       <c r="C20" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D20" t="s">
+        <v>708</v>
+      </c>
+      <c r="E20" t="s">
+        <v>707</v>
+      </c>
+      <c r="G20" t="s">
         <v>710</v>
-      </c>
-      <c r="E20" t="s">
-        <v>709</v>
-      </c>
-      <c r="G20" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>527</v>
+      </c>
+      <c r="B21" t="s">
         <v>528</v>
       </c>
-      <c r="B21" t="s">
-        <v>529</v>
-      </c>
       <c r="C21" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D21" t="s">
+        <v>708</v>
+      </c>
+      <c r="E21" t="s">
+        <v>543</v>
+      </c>
+      <c r="G21" t="s">
         <v>710</v>
-      </c>
-      <c r="E21" t="s">
-        <v>544</v>
-      </c>
-      <c r="G21" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B22" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C22" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
         <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G22" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -8543,65 +8559,65 @@
         <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C23" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E23" t="s">
         <v>119</v>
       </c>
       <c r="F23" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G23" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B24" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C24" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G24" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -8651,7 +8667,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -8661,10 +8677,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -8676,415 +8692,415 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>88</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>222</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>227</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>234</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>243</v>
-      </c>
       <c r="E16" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>249</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>250</v>
       </c>
       <c r="F18" s="9"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N21" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="G22" s="18" t="s">
         <v>252</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>253</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
       <c r="J22" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>255</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>256</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>90</v>
       </c>
       <c r="E23" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>257</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>258</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M23" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="N23" s="18" t="s">
         <v>260</v>
-      </c>
-      <c r="N23" s="18" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B24" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="D24" s="19" t="s">
         <v>715</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="E24" s="19" t="s">
         <v>716</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="E24" s="19" t="s">
+      <c r="F24" s="19" t="s">
+        <v>721</v>
+      </c>
+      <c r="J24" s="19" t="s">
         <v>718</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>723</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>720</v>
       </c>
       <c r="K24" s="19" t="b">
         <v>0</v>
@@ -9096,27 +9112,27 @@
         <v>5</v>
       </c>
       <c r="N24" s="19" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>714</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>715</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>715</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>716</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>717</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>722</v>
-      </c>
       <c r="F25" s="19" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="K25" s="19" t="b">
         <v>0</v>
@@ -9128,27 +9144,27 @@
         <v>5</v>
       </c>
       <c r="N25" s="19" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C26" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>724</v>
       </c>
-      <c r="D26" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>726</v>
-      </c>
       <c r="J26" s="19" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K26" s="19" t="b">
         <v>1</v>
@@ -9162,22 +9178,22 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D27" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>725</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>727</v>
-      </c>
       <c r="J27" s="19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="K27" s="19" t="b">
         <v>1</v>
@@ -9191,22 +9207,22 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="K28" s="19" t="b">
         <v>1</v>
@@ -9220,19 +9236,19 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="K29" s="19" t="b">
         <v>1</v>
@@ -9246,22 +9262,22 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
+        <v>732</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>734</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>715</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>735</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E30" s="19" t="s">
+      <c r="J30" s="19" t="s">
         <v>736</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>738</v>
       </c>
       <c r="K30" s="19" t="b">
         <v>1</v>
@@ -9275,19 +9291,19 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C31" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>735</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>737</v>
       </c>
       <c r="K31" s="19" t="b">
         <v>1</v>
@@ -9301,22 +9317,22 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
+        <v>737</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>715</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>745</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>741</v>
-      </c>
       <c r="J32" s="19" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="K32" s="19" t="b">
         <v>1</v>
@@ -9330,19 +9346,19 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
+        <v>738</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>743</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E33" s="19" t="s">
         <v>740</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>715</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>745</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>742</v>
       </c>
       <c r="K33" s="19" t="b">
         <v>1</v>
@@ -9356,22 +9372,22 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C34" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>741</v>
+      </c>
+      <c r="J34" s="19" t="s">
         <v>746</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>743</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>748</v>
       </c>
       <c r="K34" s="19" t="b">
         <v>1</v>
@@ -9385,19 +9401,19 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="K35" s="19" t="b">
         <v>1</v>
@@ -9411,22 +9427,22 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="K36" s="19" t="b">
         <v>1</v>
@@ -9440,22 +9456,22 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>713</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>722</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>749</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>715</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>724</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>751</v>
-      </c>
       <c r="J37" s="19" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="K37" s="19" t="b">
         <v>1</v>
@@ -9469,22 +9485,22 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="K38" s="19" t="b">
         <v>1</v>
@@ -9498,19 +9514,19 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K39" s="19" t="b">
         <v>1</v>
@@ -9522,27 +9538,27 @@
         <v>10</v>
       </c>
       <c r="N39" s="19" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B40" s="19" t="s">
+        <v>755</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>733</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>723</v>
+      </c>
+      <c r="E40" t="s">
+        <v>759</v>
+      </c>
+      <c r="J40" s="19" t="s">
         <v>757</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>735</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="E40" t="s">
-        <v>761</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>759</v>
       </c>
       <c r="K40" s="19" t="b">
         <v>0</v>
@@ -9554,27 +9570,27 @@
         <v>10</v>
       </c>
       <c r="N40" s="19" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E41" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="K41" s="19" t="b">
         <v>0</v>
@@ -9586,24 +9602,24 @@
         <v>10</v>
       </c>
       <c r="N41" s="19" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E42" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="K42" s="19" t="b">
         <v>0</v>
@@ -9615,7 +9631,7 @@
         <v>10</v>
       </c>
       <c r="N42" s="19" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -9656,7 +9672,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -9666,10 +9682,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -9681,113 +9697,113 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D6" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>114</v>
@@ -9796,127 +9812,127 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>280</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>281</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>287</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>289</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -9958,7 +9974,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -9968,10 +9984,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -9983,79 +9999,79 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>301</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>305</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>306</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>143</v>
@@ -10064,34 +10080,34 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>308</v>
-      </c>
       <c r="E9" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>309</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>310</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>154</v>
@@ -10100,57 +10116,57 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -10192,7 +10208,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10202,10 +10218,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -10217,208 +10233,208 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>320</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>325</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>328</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>329</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>331</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>332</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>335</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>337</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>343</v>
-      </c>
       <c r="E13" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>345</v>
-      </c>
       <c r="E14" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -10460,7 +10476,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10470,10 +10486,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -10485,188 +10501,188 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>350</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>351</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>357</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>359</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>360</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>363</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>368</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>369</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E14" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -10677,8 +10693,9 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10708,7 +10725,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10718,10 +10735,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -10733,188 +10750,188 @@
         <v>82</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>376</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>175</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>101</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>383</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>385</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>386</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="E10" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>362</v>
-      </c>
       <c r="E11" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="E14" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F14" s="9"/>
     </row>
